--- a/scripts/problem-bank-import.xlsx
+++ b/scripts/problem-bank-import.xlsx
@@ -152,7 +152,7 @@
     <t>당신이 기르는  애완동물들조차도  당신이  어떤 종류의  사람인지를  어느 정도 보여줍니다.</t>
   </si>
   <si>
-    <t>What he need is money.</t>
+    <t>What he needs is money.</t>
   </si>
   <si>
     <t>기르다</t>
@@ -206,7 +206,7 @@
     <t>이런 검사들  중 하나는  DAPR 검사입니다.</t>
   </si>
   <si>
-    <t>The thing which he need is money.</t>
+    <t>The thing which he needs is money.</t>
   </si>
   <si>
     <t>somehow</t>
@@ -239,7 +239,7 @@
     <t>기초단어 여부</t>
   </si>
   <si>
-    <t>The thing that he need is money.</t>
+    <t>The thing that he needs is money.</t>
   </si>
   <si>
     <t>심지어</t>
@@ -251,7 +251,7 @@
     <t>be related to</t>
   </si>
   <si>
-    <t>The thing what he need is money.</t>
+    <t>The thing what he needs is money.</t>
   </si>
   <si>
     <t>~와 관련있다</t>
@@ -308,7 +308,7 @@
     <t>의사들은 다양한 그림 그리기 검사를 사용해 오고 있습니다.</t>
   </si>
   <si>
-    <t>That he need is money.</t>
+    <t>That he needs is money.</t>
   </si>
   <si>
     <t>study</t>
